--- a/漢字（かんじ）/a.xlsx
+++ b/漢字（かんじ）/a.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="あ" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="243">
   <si>
     <t>仮名</t>
   </si>
@@ -810,6 +810,19 @@
 音響｜おんきょう
 声音｜せいおん
 静音｜せいおん</t>
+  </si>
+  <si>
+    <t>屋</t>
+  </si>
+  <si>
+    <t>屋外｜おくがい
+屋外広告物｜おくがいこうこくぶつ</t>
+  </si>
+  <si>
+    <t>穏</t>
+  </si>
+  <si>
+    <t>不穏当｜ふおんとう</t>
   </si>
   <si>
     <t>おも</t>
@@ -840,19 +853,6 @@
     </r>
   </si>
   <si>
-    <t>穏</t>
-  </si>
-  <si>
-    <t>不穏当｜ふおんとう</t>
-  </si>
-  <si>
-    <t>おと</t>
-  </si>
-  <si>
-    <t>物音｜ものおと
-雑音｜ざつおん</t>
-  </si>
-  <si>
     <t>おお</t>
   </si>
   <si>
@@ -864,7 +864,11 @@
 大雑把｜おおざっぱ</t>
   </si>
   <si>
-    <t>男</t>
+    <t>おと</t>
+  </si>
+  <si>
+    <t>物音｜ものおと
+雑音｜ざつおん</t>
   </si>
   <si>
     <t>おや</t>
@@ -879,19 +883,22 @@
 親類｜おやるい</t>
   </si>
   <si>
+    <t>男</t>
+  </si>
+  <si>
+    <t>おう</t>
+  </si>
+  <si>
+    <t>横</t>
+  </si>
+  <si>
+    <t>横断｜どうだん</t>
+  </si>
+  <si>
     <t>親挨拶｜おやあいさつ
 母親｜あはおや
 父親｜ちちおや
 親子｜おやこ</t>
-  </si>
-  <si>
-    <t>おう</t>
-  </si>
-  <si>
-    <t>横</t>
-  </si>
-  <si>
-    <t>横断｜どうだん</t>
   </si>
   <si>
     <t>往</t>
@@ -1561,10 +1568,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2017,7 +2027,7 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2780,7 +2790,7 @@
       <c r="E4" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>178</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -2961,7 +2971,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="31.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="24.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="36.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" spans="1:7">
@@ -3014,33 +3024,33 @@
       <c r="C3" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F3" t="s">
         <v>219</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:7">
+    </row>
+    <row r="4" ht="29.4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>211</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>225</v>
       </c>
     </row>
@@ -3054,64 +3064,73 @@
       <c r="C5" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>229</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="7" ht="72" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="7" ht="18" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>236</v>
+      <c r="G7" s="2" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="8" ht="36" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" ht="126" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/a.xlsx
+++ b/漢字（かんじ）/a.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="あ" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,8 @@
 図案｜ずあん
 立案｜りつあん
 答案｜とうあん
-答案用紙｜とうあんようし</t>
+答案用紙｜とうあんようし
+提案｜ていあん</t>
   </si>
   <si>
     <t>あさ</t>
@@ -730,7 +731,8 @@
     <t>園</t>
   </si>
   <si>
-    <t>公園｜こうえん</t>
+    <t>公園｜こうえん
+園芸｜えんげい</t>
   </si>
   <si>
     <t>苑</t>
@@ -1568,7 +1570,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1582,6 +1584,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1905,7 +1910,7 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="23.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="7" max="7" width="26.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2027,7 +2032,7 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2883,14 +2888,14 @@
         <v>197</v>
       </c>
     </row>
-    <row r="12" ht="18" spans="1:7">
+    <row r="12" ht="36" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="7" t="s">
         <v>199</v>
       </c>
     </row>

--- a/漢字（かんじ）/a.xlsx
+++ b/漢字（かんじ）/a.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="あ" sheetId="1" r:id="rId1"/>
@@ -351,7 +351,8 @@
     <t>維</t>
   </si>
   <si>
-    <t>維持｜いじ</t>
+    <t>維持｜いじ
+繊維｜せんい</t>
   </si>
   <si>
     <t>いち</t>
@@ -2371,7 +2372,7 @@
       <c r="B11" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="7" t="s">
         <v>90</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -2895,7 +2896,7 @@
       <c r="B12" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="2" t="s">
         <v>199</v>
       </c>
     </row>
